--- a/reports/TDM_Mall_Washroom_Details_2026.xlsx
+++ b/reports/TDM_Mall_Washroom_Details_2026.xlsx
@@ -13,7 +13,18 @@
     <sheet name="Handicap Washroom Details" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Washroom Assets Summery" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Mall Washroom Deatils'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Mall Washroom Deatils'!$A$1:$AE$65</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Staff Washroom Deatils'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Staff Washroom Deatils'!$A$1:$T$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Baby Room Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Baby Room Details'!$A$1:$X$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Handicap Washroom Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Handicap Washroom Details'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Washroom Assets Summery'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Washroom Assets Summery'!$A$1:$H$20</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -93,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -162,6 +173,12 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -195,13 +212,13 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -567,7 +584,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AE65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6918,6 +6935,7 @@
     <mergeCell ref="R1:R2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6925,7 +6943,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7957,6 +7975,7 @@
     <mergeCell ref="R1:R2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7964,7 +7983,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9605,6 +9624,7 @@
     <mergeCell ref="R1:R2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -9612,7 +9632,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -10290,6 +10310,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -10297,7 +10318,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -10626,6 +10647,8 @@
       </c>
       <c r="H12" s="11" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
@@ -10696,5 +10719,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>